--- a/artfynd/A 29822-2026 artfynd.xlsx
+++ b/artfynd/A 29822-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065305</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065302</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065307</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065321</t>
         </is>
       </c>
     </row>
@@ -1236,6 +1261,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065315</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065319</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065324</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065300</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1708,6 +1753,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065301</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065306</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1956,6 +2011,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065308</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2080,6 +2140,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065309</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2201,6 +2266,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065311</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2325,6 +2395,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065314</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2449,6 +2524,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065320</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2573,6 +2653,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065322</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2697,6 +2782,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2821,6 +2911,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065326</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2937,8 +3032,34 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135065317</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29822-2026 artfynd.xlsx
+++ b/artfynd/A 29822-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135065305</v>
       </c>
       <c r="B2" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135065302</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135065307</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135065321</v>
       </c>
       <c r="B5" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135065315</v>
       </c>
       <c r="B6" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135065319</v>
       </c>
       <c r="B7" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>135065324</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>135065300</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>135065301</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>135065306</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135065308</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>135065309</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>135065311</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>135065314</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>135065320</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>135065322</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>135065323</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>135065326</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>135065317</v>
       </c>
       <c r="B20" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 29822-2026 artfynd.xlsx
+++ b/artfynd/A 29822-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135065305</v>
       </c>
       <c r="B2" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135065302</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135065307</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>135065321</v>
       </c>
       <c r="B5" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>135065315</v>
       </c>
       <c r="B6" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>135065319</v>
       </c>
       <c r="B7" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
